--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261012.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,322,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>2,322,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
